--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TempCharacterCreatData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -19,10 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
-  <si>
-    <t>level</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>creatName</t>
   </si>
@@ -58,6 +55,25 @@
   <si>
     <t>1000,2000</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>住宅区人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022,5024,5025,5026,5028,5029,5030,5032</t>
   </si>
 </sst>
 </file>
@@ -389,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F4"/>
+  <dimension ref="A2:F5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
@@ -400,42 +416,42 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -443,16 +459,33 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
-      <c r="F4">
-        <v>5001</v>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>creatName</t>
   </si>
@@ -33,9 +33,6 @@
     <t>tempCharacters</t>
   </si>
   <si>
-    <t>tempGroupCharacters</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -66,10 +63,6 @@
   </si>
   <si>
     <t>住宅区人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -405,38 +398,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F5"/>
+  <dimension ref="A2:E5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="3" max="3" width="16.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.625" customWidth="1"/>
-    <col min="5" max="6" width="16.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
@@ -450,42 +440,36 @@
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="57" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1000</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>15</v>
+      <c r="E5" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="TempCharacterCreatData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
   <si>
     <t>creatName</t>
   </si>
   <si>
-    <t>cd</t>
-  </si>
-  <si>
     <t>maxCharacterCount</t>
   </si>
   <si>
@@ -37,23 +35,12 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>int2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>测试消费</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000,2000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -66,7 +53,134 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022,5024,5025,5026,5028,5029,5030,5032</t>
+    <t>nt[]</t>
+  </si>
+  <si>
+    <t>cds</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int[] </t>
+  </si>
+  <si>
+    <t>tempTimeRanges</t>
+  </si>
+  <si>
+    <t>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0,23,0,24,0,0,0,2,0,2,0,6,0</t>
+  </si>
+  <si>
+    <t>8,16,4,8,6,12,8,16,16,32,32,64,600,600</t>
+  </si>
+  <si>
+    <t>老公公</t>
+  </si>
+  <si>
+    <t>老英雄</t>
+  </si>
+  <si>
+    <t>小孩</t>
+  </si>
+  <si>
+    <t>小花</t>
+  </si>
+  <si>
+    <t>小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匪徒</t>
+  </si>
+  <si>
+    <t>格斗家</t>
+  </si>
+  <si>
+    <t>官员</t>
+  </si>
+  <si>
+    <t>贵族骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女轻战士</t>
+  </si>
+  <si>
+    <t>女战士</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>轻战士</t>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>双辫女孩</t>
+  </si>
+  <si>
+    <t>兔女郎</t>
+  </si>
+  <si>
+    <t>武士</t>
+  </si>
+  <si>
+    <t>小混混</t>
+  </si>
+  <si>
+    <t>小美</t>
+  </si>
+  <si>
+    <t>小男孩</t>
+  </si>
+  <si>
+    <t>小男孩2</t>
+  </si>
+  <si>
+    <t>小女孩</t>
+  </si>
+  <si>
+    <t>小女孩2</t>
+  </si>
+  <si>
+    <t>异国女子</t>
+  </si>
+  <si>
+    <t>勇者男</t>
+  </si>
+  <si>
+    <t>勇者女</t>
+  </si>
+  <si>
+    <t>游侠</t>
+  </si>
+  <si>
+    <t>战斗学者</t>
+  </si>
+  <si>
+    <t>侦探</t>
+  </si>
+  <si>
+    <t>制服小孩</t>
+  </si>
+  <si>
+    <t>重装女战士</t>
+  </si>
+  <si>
+    <t>重装战士</t>
+  </si>
+  <si>
+    <t>老公公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50000,50001,50002,50003,50004,50005,0</t>
+  </si>
+  <si>
+    <t>gameTimeRanges</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -109,13 +223,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -398,78 +508,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E5"/>
+  <dimension ref="A2:G5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="3" width="16.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.625" customWidth="1"/>
-    <col min="5" max="5" width="29.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="4" max="4" width="26" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="C4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1000</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="C5">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -477,4 +616,624 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="D3:AH29"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="12" width="3.5" customWidth="1"/>
+    <col min="18" max="18" width="27.125" customWidth="1"/>
+    <col min="20" max="20" width="8.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:34" x14ac:dyDescent="0.2">
+      <c r="D3" t="str">
+        <f>E3</f>
+        <v>6,0,8,0</v>
+      </c>
+      <c r="E3" t="str">
+        <f>F3&amp;","&amp;G3&amp;","&amp;H3&amp;","&amp;I3</f>
+        <v>6,0,8,0</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>8</v>
+      </c>
+      <c r="O3">
+        <v>16</v>
+      </c>
+      <c r="Q3" t="str">
+        <f>N3&amp;","&amp;O3</f>
+        <v>8,16</v>
+      </c>
+      <c r="R3" t="str">
+        <f>Q3</f>
+        <v>8,16</v>
+      </c>
+      <c r="T3">
+        <v>50000</v>
+      </c>
+      <c r="U3">
+        <f>T3</f>
+        <v>50000</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="4:34" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="D4" t="str">
+        <f>D3&amp;","&amp;E4</f>
+        <v>6,0,8,0,8,0,17,0</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" ref="E4:E9" si="0">F4&amp;","&amp;G4&amp;","&amp;H4&amp;","&amp;I4</f>
+        <v>8,0,17,0</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>17</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="str">
+        <f t="shared" ref="Q4:Q9" si="1">N4&amp;","&amp;O4</f>
+        <v>4,8</v>
+      </c>
+      <c r="R4" t="str">
+        <f>R3&amp;","&amp;Q4</f>
+        <v>8,16,4,8</v>
+      </c>
+      <c r="T4">
+        <v>50001</v>
+      </c>
+      <c r="U4" t="str">
+        <f>U3&amp;","&amp;T4</f>
+        <v>50000,50001</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="4:34" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="D5" t="str">
+        <f t="shared" ref="D5:D9" si="2">D4&amp;","&amp;E5</f>
+        <v>6,0,8,0,8,0,17,0,17,0,19,0</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v>17,0,19,0</v>
+      </c>
+      <c r="F5">
+        <v>17</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>6</v>
+      </c>
+      <c r="O5">
+        <v>12</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" si="1"/>
+        <v>6,12</v>
+      </c>
+      <c r="R5" t="str">
+        <f t="shared" ref="R5:R9" si="3">R4&amp;","&amp;Q5</f>
+        <v>8,16,4,8,6,12</v>
+      </c>
+      <c r="T5">
+        <v>50002</v>
+      </c>
+      <c r="U5" t="str">
+        <f t="shared" ref="U5:U9" si="4">U4&amp;","&amp;T5</f>
+        <v>50000,50001,50002</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="4:34" x14ac:dyDescent="0.2">
+      <c r="D6" t="str">
+        <f t="shared" si="2"/>
+        <v>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>19,0,23,0</v>
+      </c>
+      <c r="F6">
+        <v>19</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>23</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>8</v>
+      </c>
+      <c r="O6">
+        <v>16</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" si="1"/>
+        <v>8,16</v>
+      </c>
+      <c r="R6" t="str">
+        <f t="shared" si="3"/>
+        <v>8,16,4,8,6,12,8,16</v>
+      </c>
+      <c r="T6">
+        <v>50003</v>
+      </c>
+      <c r="U6" t="str">
+        <f t="shared" si="4"/>
+        <v>50000,50001,50002,50003</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="4:34" x14ac:dyDescent="0.2">
+      <c r="D7" t="str">
+        <f t="shared" si="2"/>
+        <v>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0,23,0,24,0</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>23,0,24,0</v>
+      </c>
+      <c r="F7">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>16</v>
+      </c>
+      <c r="O7">
+        <v>32</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" si="1"/>
+        <v>16,32</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" si="3"/>
+        <v>8,16,4,8,6,12,8,16,16,32</v>
+      </c>
+      <c r="T7">
+        <v>50004</v>
+      </c>
+      <c r="U7" t="str">
+        <f t="shared" si="4"/>
+        <v>50000,50001,50002,50003,50004</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="4:34" x14ac:dyDescent="0.2">
+      <c r="D8" t="str">
+        <f t="shared" si="2"/>
+        <v>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0,23,0,24,0,0,0,2,0</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>0,0,2,0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>32</v>
+      </c>
+      <c r="O8">
+        <v>64</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="1"/>
+        <v>32,64</v>
+      </c>
+      <c r="R8" t="str">
+        <f t="shared" si="3"/>
+        <v>8,16,4,8,6,12,8,16,16,32,32,64</v>
+      </c>
+      <c r="T8">
+        <v>50005</v>
+      </c>
+      <c r="U8" t="str">
+        <f t="shared" si="4"/>
+        <v>50000,50001,50002,50003,50004,50005</v>
+      </c>
+      <c r="V8" t="s">
+        <v>21</v>
+      </c>
+      <c r="W8" t="s">
+        <v>22</v>
+      </c>
+      <c r="X8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="4:34" x14ac:dyDescent="0.2">
+      <c r="D9" t="str">
+        <f t="shared" si="2"/>
+        <v>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0,23,0,24,0,0,0,2,0,2,0,6,0</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>2,0,6,0</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>600</v>
+      </c>
+      <c r="O9">
+        <v>600</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="1"/>
+        <v>600,600</v>
+      </c>
+      <c r="R9" t="str">
+        <f t="shared" si="3"/>
+        <v>8,16,4,8,6,12,8,16,16,32,32,64,600,600</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" t="str">
+        <f t="shared" si="4"/>
+        <v>50000,50001,50002,50003,50004,50005,0</v>
+      </c>
+      <c r="V9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="U19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="U20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="18:25" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="R25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R27" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R28" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="R29" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -37,10 +37,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>测试消费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,6 +176,10 @@
   </si>
   <si>
     <t>gameTimeRanges</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试消费</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -521,7 +521,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -530,21 +530,21 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
@@ -553,13 +553,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>2</v>
@@ -570,22 +570,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
@@ -593,22 +593,22 @@
         <v>1000</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -671,31 +671,31 @@
         <v>50000</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y3" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="Z3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="4:34" ht="28.5" x14ac:dyDescent="0.2">
@@ -741,43 +741,43 @@
         <v>50000,50001</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="X4" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="Y4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AB4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AC4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE4" s="1" t="s">
+      <c r="AF4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AF4" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="AG4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH4" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="4:34" ht="28.5" x14ac:dyDescent="0.2">
@@ -823,43 +823,43 @@
         <v>50000,50001,50002</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="Y5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Y5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA5" s="1" t="s">
+      <c r="AC5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AB5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD5" s="1" t="s">
+      <c r="AE5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AE5" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="AF5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AG5" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="AH5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="4:34" x14ac:dyDescent="0.2">
@@ -905,40 +905,40 @@
         <v>50000,50001,50002,50003</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="X6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Z6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="AA6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG6" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="4:34" x14ac:dyDescent="0.2">
@@ -984,28 +984,28 @@
         <v>50000,50001,50002,50003,50004</v>
       </c>
       <c r="V7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X7" s="1" t="s">
+      <c r="Y7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="Z7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AB7" s="1" t="s">
+      <c r="AC7" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="4:34" x14ac:dyDescent="0.2">
@@ -1051,22 +1051,22 @@
         <v>50000,50001,50002,50003,50004,50005</v>
       </c>
       <c r="V8" t="s">
+        <v>20</v>
+      </c>
+      <c r="W8" t="s">
         <v>21</v>
       </c>
-      <c r="W8" t="s">
-        <v>22</v>
-      </c>
       <c r="X8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z8" t="s">
         <v>42</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AA8" t="s">
         <v>43</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="4:34" x14ac:dyDescent="0.2">
@@ -1112,123 +1112,123 @@
         <v>50000,50001,50002,50003,50004,50005,0</v>
       </c>
       <c r="V9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="18:25" x14ac:dyDescent="0.2">
       <c r="U19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="18:25" x14ac:dyDescent="0.2">
       <c r="U20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="18:25" ht="28.5" x14ac:dyDescent="0.2">
       <c r="R25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R28" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="18:25" x14ac:dyDescent="0.2">
       <c r="R29" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="57">
   <si>
     <t>creatName</t>
   </si>
@@ -181,6 +181,24 @@
   <si>
     <t>测试消费</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>路人男</t>
+  </si>
+  <si>
+    <t>中年路人女</t>
+  </si>
+  <si>
+    <t>中年路人男</t>
+  </si>
+  <si>
+    <t>红发小孩</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
   </si>
 </sst>
 </file>
@@ -203,12 +221,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -223,11 +253,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -620,15 +654,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="D3:AH29"/>
+  <dimension ref="D3:AN29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="12" width="3.5" customWidth="1"/>
     <col min="18" max="18" width="27.125" customWidth="1"/>
-    <col min="20" max="20" width="8.875" customWidth="1"/>
+    <col min="20" max="20" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="4:40" x14ac:dyDescent="0.2">
       <c r="D3" t="str">
         <f>E3</f>
         <v>6,0,8,0</v>
@@ -673,7 +707,7 @@
       <c r="V3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="X3" s="1" t="s">
@@ -691,14 +725,20 @@
       <c r="AB3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AC3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AD3" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="4:34" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="AF3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="4:40" ht="28.5" x14ac:dyDescent="0.2">
       <c r="D4" t="str">
         <f>D3&amp;","&amp;E4</f>
         <v>6,0,8,0,8,0,17,0</v>
@@ -767,20 +807,32 @@
       <c r="AD4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AE4" s="1" t="s">
+      <c r="AE4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AF4" s="1" t="s">
+      <c r="AF4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AG4" s="1" t="s">
+      <c r="AG4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AH4" s="1" t="s">
+      <c r="AH4" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="4:34" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="AI4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="4:40" ht="28.5" x14ac:dyDescent="0.2">
       <c r="D5" t="str">
         <f t="shared" ref="D5:D9" si="2">D4&amp;","&amp;E5</f>
         <v>6,0,8,0,8,0,17,0,17,0,19,0</v>
@@ -852,17 +904,35 @@
       <c r="AE5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AF5" s="1" t="s">
+      <c r="AF5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AG5" s="1" t="s">
+      <c r="AG5" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AH5" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="4:34" x14ac:dyDescent="0.2">
+      <c r="AI5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AM5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN5" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="4:40" x14ac:dyDescent="0.2">
       <c r="D6" t="str">
         <f t="shared" si="2"/>
         <v>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0</v>
@@ -940,8 +1010,26 @@
       <c r="AG6" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="4:34" x14ac:dyDescent="0.2">
+      <c r="AH6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM6" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="4:40" x14ac:dyDescent="0.2">
       <c r="D7" t="str">
         <f t="shared" si="2"/>
         <v>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0,23,0,24,0</v>
@@ -1007,8 +1095,20 @@
       <c r="AC7" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8" spans="4:34" x14ac:dyDescent="0.2">
+      <c r="AD7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="4:40" x14ac:dyDescent="0.2">
       <c r="D8" t="str">
         <f t="shared" si="2"/>
         <v>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0,23,0,24,0,0,0,2,0</v>
@@ -1068,8 +1168,14 @@
       <c r="AA8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="4:34" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="4:40" x14ac:dyDescent="0.2">
       <c r="D9" t="str">
         <f t="shared" si="2"/>
         <v>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0,23,0,24,0,0,0,2,0,2,0,6,0</v>

--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="69">
   <si>
     <t>creatName</t>
   </si>
@@ -199,6 +199,48 @@
   </si>
   <si>
     <t>黄衣服小女孩</t>
+  </si>
+  <si>
+    <t>广场人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店街人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>码头人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50006,50007,50008,50009,50010,50011,0</t>
+  </si>
+  <si>
+    <t>50012,50013,50014,50015,50016,50017,0</t>
+  </si>
+  <si>
+    <t>50018,50019,50020,50021,50022,50023,0</t>
+  </si>
+  <si>
+    <t>城门人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坡道人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后山人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50024,50025,50026,50027,50028,50029,0</t>
+  </si>
+  <si>
+    <t>50030,50031,50032,50033,50034,50035,0</t>
+  </si>
+  <si>
+    <t>50036,50037,50038,50039,50040,50041,0</t>
   </si>
 </sst>
 </file>
@@ -542,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G5"/>
+  <dimension ref="A2:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
@@ -550,7 +592,7 @@
     <col min="4" max="4" width="26" style="1" customWidth="1"/>
     <col min="5" max="5" width="29.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="35.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.625" customWidth="1"/>
+    <col min="7" max="7" width="16.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -572,7 +614,7 @@
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -643,6 +685,144 @@
       </c>
       <c r="G5" s="1" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1001</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1002</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1003</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1004</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1005</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1006</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1221,7 +1401,25 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="18:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="AE15">
+        <v>50036</v>
+      </c>
+      <c r="AF15">
+        <f>AE15</f>
+        <v>50036</v>
+      </c>
+    </row>
+    <row r="16" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="AE16">
+        <v>50037</v>
+      </c>
+      <c r="AF16" t="str">
+        <f>AF15&amp;","&amp;AE16</f>
+        <v>50036,50037</v>
+      </c>
+    </row>
+    <row r="17" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1234,8 +1432,15 @@
       <c r="Y17" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="AE17">
+        <v>50038</v>
+      </c>
+      <c r="AF17" t="str">
+        <f t="shared" ref="AF17:AF21" si="5">AF16&amp;","&amp;AE17</f>
+        <v>50036,50037,50038</v>
+      </c>
+    </row>
+    <row r="18" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1248,8 +1453,15 @@
       <c r="Y18" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="AE18">
+        <v>50039</v>
+      </c>
+      <c r="AF18" t="str">
+        <f t="shared" si="5"/>
+        <v>50036,50037,50038,50039</v>
+      </c>
+    </row>
+    <row r="19" spans="18:32" x14ac:dyDescent="0.2">
       <c r="U19" s="1" t="s">
         <v>20</v>
       </c>
@@ -1259,24 +1471,45 @@
       <c r="Y19" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="AE19">
+        <v>50040</v>
+      </c>
+      <c r="AF19" t="str">
+        <f t="shared" si="5"/>
+        <v>50036,50037,50038,50039,50040</v>
+      </c>
+    </row>
+    <row r="20" spans="18:32" x14ac:dyDescent="0.2">
       <c r="U20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="Y20" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="AE20">
+        <v>50041</v>
+      </c>
+      <c r="AF20" t="str">
+        <f t="shared" si="5"/>
+        <v>50036,50037,50038,50039,50040,50041</v>
+      </c>
+    </row>
+    <row r="21" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="U21" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="18:25" x14ac:dyDescent="0.2">
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="str">
+        <f t="shared" si="5"/>
+        <v>50036,50037,50038,50039,50040,50041,0</v>
+      </c>
+    </row>
+    <row r="22" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R22" s="1" t="s">
         <v>18</v>
       </c>
@@ -1284,7 +1517,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="18:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1295,7 +1528,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="18:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R24" s="1" t="s">
         <v>33</v>
       </c>
@@ -1306,7 +1539,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="18:25" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="18:32" ht="28.5" x14ac:dyDescent="0.2">
       <c r="R25" s="1" t="s">
         <v>34</v>
       </c>
@@ -1314,7 +1547,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="18:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R26" s="1" t="s">
         <v>35</v>
       </c>
@@ -1322,17 +1555,17 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="18:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R27" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="18:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R28" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="18:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R29" s="1" t="s">
         <v>44</v>
       </c>

--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -649,7 +649,7 @@
         <v>50</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>13</v>
@@ -672,7 +672,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>13</v>
@@ -695,7 +695,7 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>13</v>
@@ -718,7 +718,7 @@
         <v>58</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>13</v>
@@ -741,7 +741,7 @@
         <v>59</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>13</v>
@@ -764,7 +764,7 @@
         <v>63</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>13</v>
@@ -787,7 +787,7 @@
         <v>64</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>13</v>
@@ -810,7 +810,7 @@
         <v>65</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>13</v>
@@ -828,7 +828,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
   <si>
     <t>creatName</t>
   </si>
@@ -241,6 +241,34 @@
   </si>
   <si>
     <t>50036,50037,50038,50039,50040,50041,0</t>
+  </si>
+  <si>
+    <t>酒馆人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>船坞人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大厅人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14,0,24,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,0,19,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32,64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -584,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G11"/>
+  <dimension ref="A2:G15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
@@ -672,7 +700,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>13</v>
@@ -695,7 +723,7 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>13</v>
@@ -718,7 +746,7 @@
         <v>58</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>13</v>
@@ -741,7 +769,7 @@
         <v>59</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>13</v>
@@ -764,7 +792,7 @@
         <v>63</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>13</v>
@@ -787,7 +815,7 @@
         <v>64</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>13</v>
@@ -810,7 +838,7 @@
         <v>65</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>13</v>
@@ -823,6 +851,98 @@
       </c>
       <c r="G11" s="1" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1007</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="1">
+        <v>50042</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1008</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="1">
+        <v>50043</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1009</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="1">
+        <v>50044</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1010</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="1">
+        <v>50045</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -884,7 +884,7 @@
         <v>70</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>74</v>

--- a/Datas/TempCharacterCreatData.xlsx
+++ b/Datas/TempCharacterCreatData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="87">
   <si>
     <t>creatName</t>
   </si>
@@ -28,246 +28,301 @@
     <t>maxCharacterCount</t>
   </si>
   <si>
-    <t>tempCharacters</t>
+    <t>string</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>住宅区人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老公公</t>
+  </si>
+  <si>
+    <t>老英雄</t>
+  </si>
+  <si>
+    <t>小孩</t>
+  </si>
+  <si>
+    <t>小花</t>
+  </si>
+  <si>
+    <t>小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匪徒</t>
+  </si>
+  <si>
+    <t>格斗家</t>
+  </si>
+  <si>
+    <t>官员</t>
+  </si>
+  <si>
+    <t>贵族骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女轻战士</t>
+  </si>
+  <si>
+    <t>女战士</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>轻战士</t>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>双辫女孩</t>
+  </si>
+  <si>
+    <t>兔女郎</t>
+  </si>
+  <si>
+    <t>武士</t>
+  </si>
+  <si>
+    <t>小混混</t>
+  </si>
+  <si>
+    <t>小美</t>
+  </si>
+  <si>
+    <t>小男孩</t>
+  </si>
+  <si>
+    <t>小男孩2</t>
+  </si>
+  <si>
+    <t>小女孩</t>
+  </si>
+  <si>
+    <t>小女孩2</t>
+  </si>
+  <si>
+    <t>异国女子</t>
+  </si>
+  <si>
+    <t>勇者男</t>
+  </si>
+  <si>
+    <t>勇者女</t>
+  </si>
+  <si>
+    <t>游侠</t>
+  </si>
+  <si>
+    <t>战斗学者</t>
+  </si>
+  <si>
+    <t>侦探</t>
+  </si>
+  <si>
+    <t>制服小孩</t>
+  </si>
+  <si>
+    <t>重装女战士</t>
+  </si>
+  <si>
+    <t>重装战士</t>
+  </si>
+  <si>
+    <t>老公公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>路人男</t>
+  </si>
+  <si>
+    <t>中年路人女</t>
+  </si>
+  <si>
+    <t>中年路人男</t>
+  </si>
+  <si>
+    <t>红发小孩</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
+  </si>
+  <si>
+    <t>广场人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店街人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>码头人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城门人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坡道人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后山人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒馆人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>船坞人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大厅人群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32,64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>住宅区人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nt[]</t>
-  </si>
-  <si>
-    <t>cds</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int[] </t>
-  </si>
-  <si>
-    <t>tempTimeRanges</t>
-  </si>
-  <si>
-    <t>6,0,8,0,8,0,17,0,17,0,19,0,19,0,23,0,23,0,24,0,0,0,2,0,2,0,6,0</t>
-  </si>
-  <si>
-    <t>8,16,4,8,6,12,8,16,16,32,32,64,600,600</t>
-  </si>
-  <si>
-    <t>老公公</t>
-  </si>
-  <si>
-    <t>老英雄</t>
-  </si>
-  <si>
-    <t>小孩</t>
-  </si>
-  <si>
-    <t>小花</t>
-  </si>
-  <si>
-    <t>小丑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匪徒</t>
-  </si>
-  <si>
-    <t>格斗家</t>
-  </si>
-  <si>
-    <t>官员</t>
-  </si>
-  <si>
-    <t>贵族骑士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>女轻战士</t>
-  </si>
-  <si>
-    <t>女战士</t>
-  </si>
-  <si>
-    <t>骑士</t>
-  </si>
-  <si>
-    <t>轻战士</t>
-  </si>
-  <si>
-    <t>商人</t>
-  </si>
-  <si>
-    <t>双辫女孩</t>
-  </si>
-  <si>
-    <t>兔女郎</t>
-  </si>
-  <si>
-    <t>武士</t>
-  </si>
-  <si>
-    <t>小混混</t>
-  </si>
-  <si>
-    <t>小美</t>
-  </si>
-  <si>
-    <t>小男孩</t>
-  </si>
-  <si>
-    <t>小男孩2</t>
-  </si>
-  <si>
-    <t>小女孩</t>
-  </si>
-  <si>
-    <t>小女孩2</t>
-  </si>
-  <si>
-    <t>异国女子</t>
-  </si>
-  <si>
-    <t>勇者男</t>
-  </si>
-  <si>
-    <t>勇者女</t>
-  </si>
-  <si>
-    <t>游侠</t>
-  </si>
-  <si>
-    <t>战斗学者</t>
-  </si>
-  <si>
-    <t>侦探</t>
-  </si>
-  <si>
-    <t>制服小孩</t>
-  </si>
-  <si>
-    <t>重装女战士</t>
-  </si>
-  <si>
-    <t>重装战士</t>
-  </si>
-  <si>
-    <t>老公公</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50000,50001,50002,50003,50004,50005,0</t>
-  </si>
-  <si>
-    <t>gameTimeRanges</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>TempCharacterStep:tempCharacterSteps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endTime</t>
+  </si>
+  <si>
+    <t>tempCharacter</t>
+  </si>
+  <si>
+    <t>endTempTime</t>
+  </si>
+  <si>
+    <t>startTempTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32,64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16,32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>64,128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,17</t>
+  </si>
+  <si>
+    <t>8,18</t>
   </si>
   <si>
     <t>测试消费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>路人女</t>
-  </si>
-  <si>
-    <t>路人男</t>
-  </si>
-  <si>
-    <t>中年路人女</t>
-  </si>
-  <si>
-    <t>中年路人男</t>
-  </si>
-  <si>
-    <t>红发小孩</t>
-  </si>
-  <si>
-    <t>黄衣服小女孩</t>
-  </si>
-  <si>
-    <t>广场人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>商店街人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>码头人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50006,50007,50008,50009,50010,50011,0</t>
-  </si>
-  <si>
-    <t>50012,50013,50014,50015,50016,50017,0</t>
-  </si>
-  <si>
-    <t>50018,50019,50020,50021,50022,50023,0</t>
-  </si>
-  <si>
-    <t>城门人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坡道人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>后山人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50024,50025,50026,50027,50028,50029,0</t>
-  </si>
-  <si>
-    <t>50030,50031,50032,50033,50034,50035,0</t>
-  </si>
-  <si>
-    <t>50036,50037,50038,50039,50040,50041,0</t>
-  </si>
-  <si>
-    <t>酒馆人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教堂人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>船坞人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大厅人群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14,0,24,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,0,19,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>32,64</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -323,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -332,6 +387,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -612,337 +672,1054 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G15"/>
+  <dimension ref="A2:I43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="4" width="26" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="1" customWidth="1"/>
+    <col min="4" max="6" width="10.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="1" customWidth="1"/>
+    <col min="8" max="9" width="10.5" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="1">
+        <v>50100</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="1">
+        <v>50101</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="1">
+        <v>50101</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="1">
+        <v>50102</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="1">
+        <v>50103</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="1">
+        <v>50104</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="1">
+        <v>50104</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="1">
+        <v>50001</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="1">
+        <v>50002</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="1">
+        <v>50003</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="1">
+        <v>50006</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="1">
+        <v>50007</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="1">
+        <v>50008</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="1">
+        <v>50009</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="1">
+        <v>50012</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="1">
+        <v>50013</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C22" s="1">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="1">
+        <v>50014</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C23" s="1">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="1">
+        <v>50015</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" s="1">
+        <v>50018</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="1">
+        <v>50019</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C26" s="1">
+        <v>2</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="1">
+        <v>50020</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="1">
+        <v>50021</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28" s="1">
+        <v>50024</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C29" s="1">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="1">
+        <v>50025</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C30" s="1">
+        <v>2</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="1">
+        <v>50026</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C31" s="1">
+        <v>2</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="1">
+        <v>50027</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="D32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" s="1">
+        <v>50030</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" s="1">
+        <v>50031</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="1">
+        <v>50032</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C35" s="1">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="1">
+        <v>50033</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" s="1">
+        <v>50030</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G37" s="1">
+        <v>50031</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" s="1">
+        <v>50032</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C39" s="1">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G39" s="1">
+        <v>50033</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>1007</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="1">
+        <v>5</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" s="4">
+        <v>50042</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>1008</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="1">
+        <v>5</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G41" s="4">
+        <v>50043</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>1009</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1000</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
+      <c r="D42" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" s="4">
+        <v>50044</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="1">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1001</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1002</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1003</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1004</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1005</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1006</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>1007</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="1">
-        <v>50042</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1008</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="1">
-        <v>50043</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1009</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="1">
-        <v>50044</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1010</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="D43" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" s="4">
         <v>50045</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1005,37 +1782,37 @@
         <v>50000</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AF3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="AG3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="4:40" ht="28.5" x14ac:dyDescent="0.2">
@@ -1081,55 +1858,55 @@
         <v>50000,50001</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Z4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE4" s="2" t="s">
+      <c r="AH4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AF4" s="2" t="s">
+      <c r="AL4" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="AG4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL4" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="5" spans="4:40" ht="28.5" x14ac:dyDescent="0.2">
@@ -1175,61 +1952,61 @@
         <v>50000,50001,50002</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z5" s="1" t="s">
+      <c r="AA5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AA5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB5" s="1" t="s">
+      <c r="AF5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AC5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD5" s="1" t="s">
+      <c r="AI5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AE5" s="1" t="s">
+      <c r="AN5" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AL5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AN5" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="4:40" x14ac:dyDescent="0.2">
@@ -1275,58 +2052,58 @@
         <v>50000,50001,50002,50003</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AA6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AB6" s="1" t="s">
+      <c r="AC6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AI6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AD6" s="1" t="s">
+      <c r="AJ6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AE6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL6" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="AM6" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="4:40" x14ac:dyDescent="0.2">
@@ -1372,40 +2149,40 @@
         <v>50000,50001,50002,50003,50004</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Z7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AA7" s="1" t="s">
+      <c r="AB7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB7" s="1" t="s">
+      <c r="AE7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AC7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE7" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="AF7" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="AG7" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="4:40" x14ac:dyDescent="0.2">
@@ -1451,28 +2228,28 @@
         <v>50000,50001,50002,50003,50004,50005</v>
       </c>
       <c r="V8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="W8" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="X8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y8" t="s">
         <v>32</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Z8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AC8" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="9" spans="4:40" x14ac:dyDescent="0.2">
@@ -1518,7 +2295,7 @@
         <v>50000,50001,50002,50003,50004,50005,0</v>
       </c>
       <c r="V9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="4:40" x14ac:dyDescent="0.2">
@@ -1541,16 +2318,16 @@
     </row>
     <row r="17" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y17" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="AE17">
         <v>50038</v>
@@ -1562,16 +2339,16 @@
     </row>
     <row r="18" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y18" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="AE18">
         <v>50039</v>
@@ -1583,13 +2360,13 @@
     </row>
     <row r="19" spans="18:32" x14ac:dyDescent="0.2">
       <c r="U19" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AE19">
         <v>50040</v>
@@ -1601,10 +2378,10 @@
     </row>
     <row r="20" spans="18:32" x14ac:dyDescent="0.2">
       <c r="U20" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AE20">
         <v>50041</v>
@@ -1616,10 +2393,10 @@
     </row>
     <row r="21" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R21" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AE21">
         <v>0</v>
@@ -1631,63 +2408,63 @@
     </row>
     <row r="22" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R22" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R23" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R24" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="18:32" ht="28.5" x14ac:dyDescent="0.2">
       <c r="R25" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R26" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R27" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R28" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="18:32" x14ac:dyDescent="0.2">
       <c r="R29" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
